--- a/INMOcambios.xlsx
+++ b/INMOcambios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador.BREVIA2015\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B408F1F4-5F8B-436B-8EB9-9B3F09237B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09E2D65-4603-471C-A222-C00C58A3D5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9645" yWindow="720" windowWidth="18825" windowHeight="14595" xr2:uid="{78DC7B37-4F50-46A2-B413-CE448765714D}"/>
+    <workbookView xWindow="2620" yWindow="2620" windowWidth="14400" windowHeight="7270" xr2:uid="{78DC7B37-4F50-46A2-B413-CE448765714D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Versión</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>Se añade gestión de cambio de estado de registro para las opciones principales.</t>
+  </si>
+  <si>
+    <t>2026.05.04-01</t>
+  </si>
+  <si>
+    <t>Cuando se creaba un nuevo registro, si la tabla estaba vacía, daba error. Se comenta la instrucción: rst.moveLast que producía el problema. Se cambia en todas las tablas principales. CLIENTE-INMUEBLE-DEMANDA-OPERACIÓN-AGENDA-DOCUMENTO</t>
   </si>
 </sst>
 </file>
@@ -64,10 +70,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -95,10 +109,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,38 +458,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71109F90-5E7C-4880-8813-6884FE174043}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="3" max="3" width="88.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>46141</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
       <c r="C3" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="4" spans="1:10" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46146</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
